--- a/data/jjj/wind.xlsx
+++ b/data/jjj/wind.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,277 +439,145 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46117.75</v>
+        <v>46166.04166666666</v>
       </c>
       <c r="B2" t="n">
-        <v>312.3</v>
+        <v>296.4999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46117.79166666666</v>
+        <v>46166.08333333334</v>
       </c>
       <c r="B3" t="n">
-        <v>343.2</v>
+        <v>118.2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46117.83333333334</v>
+        <v>46166.125</v>
       </c>
       <c r="B4" t="n">
-        <v>12.1</v>
+        <v>140.9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46117.875</v>
+        <v>46166.16666666666</v>
       </c>
       <c r="B5" t="n">
-        <v>297.9</v>
+        <v>149.2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46117.91666666666</v>
+        <v>46166.20833333334</v>
       </c>
       <c r="B6" t="n">
-        <v>343.3</v>
+        <v>170.7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46117.95833333334</v>
+        <v>46166.25</v>
       </c>
       <c r="B7" t="n">
-        <v>333.2</v>
+        <v>170.2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46118</v>
+        <v>46166.29166666666</v>
       </c>
       <c r="B8" t="n">
-        <v>301.9</v>
+        <v>160.9</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46118.04166666666</v>
+        <v>46166.33333333334</v>
       </c>
       <c r="B9" t="n">
-        <v>66.40000000000001</v>
+        <v>196.7</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46118.08333333334</v>
+        <v>46166.375</v>
       </c>
       <c r="B10" t="n">
-        <v>57.40000000000001</v>
+        <v>153.2</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46118.125</v>
+        <v>46166.41666666666</v>
       </c>
       <c r="B11" t="n">
-        <v>64.2</v>
+        <v>155.8</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46118.16666666666</v>
+        <v>46166.45833333334</v>
       </c>
       <c r="B12" t="n">
-        <v>62.6</v>
+        <v>177.4</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46118.20833333334</v>
+        <v>46166.5</v>
       </c>
       <c r="B13" t="n">
-        <v>108.4</v>
+        <v>149.2</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46118.25</v>
+        <v>46166.54166666666</v>
       </c>
       <c r="B14" t="n">
-        <v>53.1</v>
+        <v>144.7</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46118.29166666666</v>
-      </c>
-      <c r="B15" t="n">
-        <v>319.4999999999999</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46118.33333333334</v>
-      </c>
-      <c r="B16" t="n">
-        <v>305.8999999999999</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46118.375</v>
-      </c>
-      <c r="B17" t="n">
-        <v>356.9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46118.41666666666</v>
-      </c>
-      <c r="B18" t="n">
-        <v>299.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46118.45833333334</v>
-      </c>
-      <c r="B19" t="n">
-        <v>197.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46118.5</v>
-      </c>
-      <c r="B20" t="n">
-        <v>200</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46118.54166666666</v>
-      </c>
-      <c r="B21" t="n">
-        <v>183.1</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46118.58333333334</v>
-      </c>
-      <c r="B22" t="n">
-        <v>162.1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46118.625</v>
-      </c>
-      <c r="B23" t="n">
-        <v>153</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46118.66666666666</v>
-      </c>
-      <c r="B24" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="C24" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46118.70833333334</v>
-      </c>
-      <c r="B25" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46118.75</v>
-      </c>
-      <c r="B26" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/jjj/wind.xlsx
+++ b/data/jjj/wind.xlsx
@@ -439,142 +439,142 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46166.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B2" t="n">
-        <v>296.4999999999999</v>
+        <v>98.30000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46166.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B3" t="n">
-        <v>118.2</v>
+        <v>97.89999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46166.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B4" t="n">
-        <v>140.9</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46166.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B5" t="n">
-        <v>149.2</v>
+        <v>99.69999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46166.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B6" t="n">
-        <v>170.7</v>
+        <v>99.09999999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46166.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B7" t="n">
-        <v>170.2</v>
+        <v>123.3</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46166.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B8" t="n">
-        <v>160.9</v>
+        <v>153.8</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46166.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B9" t="n">
-        <v>196.7</v>
+        <v>152.3</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46166.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B10" t="n">
-        <v>153.2</v>
+        <v>160.8</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46166.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B11" t="n">
-        <v>155.8</v>
+        <v>160.6</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46166.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B12" t="n">
-        <v>177.4</v>
+        <v>156.9</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46166.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B13" t="n">
-        <v>149.2</v>
+        <v>158.8</v>
       </c>
       <c r="C13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46166.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B14" t="n">
-        <v>144.7</v>
+        <v>143</v>
       </c>
       <c r="C14" t="n">
         <v>2.3</v>

--- a/data/jjj/wind.xlsx
+++ b/data/jjj/wind.xlsx
@@ -439,145 +439,145 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46157.04166666666</v>
+        <v>46165.5</v>
       </c>
       <c r="B2" t="n">
-        <v>98.30000000000001</v>
+        <v>191.1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46157.08333333334</v>
+        <v>46165.54166666666</v>
       </c>
       <c r="B3" t="n">
-        <v>97.89999999999999</v>
+        <v>189.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46157.125</v>
+        <v>46165.58333333334</v>
       </c>
       <c r="B4" t="n">
-        <v>97.09999999999999</v>
+        <v>175.1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46157.16666666666</v>
+        <v>46165.625</v>
       </c>
       <c r="B5" t="n">
-        <v>99.69999999999999</v>
+        <v>168.9</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46157.20833333334</v>
+        <v>46165.66666666666</v>
       </c>
       <c r="B6" t="n">
-        <v>99.09999999999998</v>
+        <v>170.2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46157.25</v>
+        <v>46165.70833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>123.3</v>
+        <v>154.7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46157.29166666666</v>
+        <v>46165.75</v>
       </c>
       <c r="B8" t="n">
-        <v>153.8</v>
+        <v>138.2</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46157.33333333334</v>
+        <v>46165.79166666666</v>
       </c>
       <c r="B9" t="n">
-        <v>152.3</v>
+        <v>135.2</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46157.375</v>
+        <v>46165.83333333334</v>
       </c>
       <c r="B10" t="n">
-        <v>160.8</v>
+        <v>126</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46157.41666666666</v>
+        <v>46165.875</v>
       </c>
       <c r="B11" t="n">
-        <v>160.6</v>
+        <v>135.7</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46157.45833333334</v>
+        <v>46165.91666666666</v>
       </c>
       <c r="B12" t="n">
-        <v>156.9</v>
+        <v>124.3</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46157.5</v>
+        <v>46165.95833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>158.8</v>
+        <v>109</v>
       </c>
       <c r="C13" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46157.54166666666</v>
+        <v>46166</v>
       </c>
       <c r="B14" t="n">
-        <v>143</v>
+        <v>354.3</v>
       </c>
       <c r="C14" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/jjj/wind.xlsx
+++ b/data/jjj/wind.xlsx
@@ -439,65 +439,65 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46165.5</v>
+        <v>46145.79166666666</v>
       </c>
       <c r="B2" t="n">
-        <v>191.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46165.54166666666</v>
+        <v>46145.83333333334</v>
       </c>
       <c r="B3" t="n">
-        <v>189.1</v>
+        <v>50.99999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46165.58333333334</v>
+        <v>46145.875</v>
       </c>
       <c r="B4" t="n">
-        <v>175.1</v>
+        <v>133.3</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46165.625</v>
+        <v>46145.91666666666</v>
       </c>
       <c r="B5" t="n">
-        <v>168.9</v>
+        <v>188.7</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46165.66666666666</v>
+        <v>46145.95833333334</v>
       </c>
       <c r="B6" t="n">
-        <v>170.2</v>
+        <v>218.7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46165.70833333334</v>
+        <v>46146</v>
       </c>
       <c r="B7" t="n">
-        <v>154.7</v>
+        <v>229.9</v>
       </c>
       <c r="C7" t="n">
         <v>1.4</v>
@@ -505,79 +505,79 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46165.75</v>
+        <v>46146.04166666666</v>
       </c>
       <c r="B8" t="n">
-        <v>138.2</v>
+        <v>250.1</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46165.79166666666</v>
+        <v>46146.08333333334</v>
       </c>
       <c r="B9" t="n">
-        <v>135.2</v>
+        <v>308.6</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46146.125</v>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>307.1</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46165.875</v>
+        <v>46146.16666666666</v>
       </c>
       <c r="B11" t="n">
-        <v>135.7</v>
+        <v>307.7</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46165.91666666666</v>
+        <v>46146.20833333334</v>
       </c>
       <c r="B12" t="n">
-        <v>124.3</v>
+        <v>306.7</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46165.95833333334</v>
+        <v>46146.25</v>
       </c>
       <c r="B13" t="n">
-        <v>109</v>
+        <v>305.1999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46166</v>
+        <v>46146.29166666666</v>
       </c>
       <c r="B14" t="n">
-        <v>354.3</v>
+        <v>303.9999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
